--- a/code_mapping/[ERPiU] 8. 금융계좌매핑정의서.xlsx
+++ b/code_mapping/[ERPiU] 8. 금융계좌매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\MIG\1. GIT\공유파일\매핑정의서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="금융계좌매핑정의서" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Y</t>
   </si>
@@ -136,6 +136,10 @@
   </si>
   <si>
     <t>금융계좌매핑정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1152,8 +1156,8 @@
       <c r="B1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="26">
-        <v>20260513</v>
+      <c r="C1" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="D1" s="25"/>
       <c r="E1" s="26"/>
@@ -1358,7 +1362,7 @@
       <c r="G22" s="59"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2HkrjbdYvuCi/rJj2/NvJFpk8aTWqH8SDDuhGVsx5jF5p7m32Qep2ZtLWTZeGCMhUu1j7ATspb58J626Zr6N4A==" saltValue="kbFi8ScZCp1IPmyn1zpzyg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:G4"/>
   </mergeCells>
@@ -1589,7 +1593,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nDKIQ+5/vGZj1Aplp5BBZ/yX1+PBUKHIl05n0Lo+ernDWDS8UEE7vlYSphx0ez+rxF2ZebreEtLTDRSAUqKRgg==" saltValue="wv9CoeEwrZYxfVnWVlAcMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G3"/>
   </mergeCells>
